--- a/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
+++ b/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="809">
   <si>
-    <t xml:space="preserve">File creation date: 12/09/2026</t>
+    <t xml:space="preserve">File creation date: 13/09/2026</t>
   </si>
   <si>
     <t xml:space="preserve">ANNEX IV,Last update: 11/09/2026</t>

--- a/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
+++ b/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="809">
   <si>
-    <t xml:space="preserve">File creation date: 13/09/2026</t>
+    <t xml:space="preserve">File creation date: 14/09/2026</t>
   </si>
   <si>
     <t xml:space="preserve">ANNEX IV,Last update: 11/09/2026</t>

--- a/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
+++ b/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
@@ -22,10 +22,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="809">
   <si>
-    <t xml:space="preserve">File creation date: 14/09/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANNEX IV,Last update: 11/09/2026</t>
+    <t xml:space="preserve">File creation date: 15/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANNEX IV,Last update: 14/09/2026</t>
   </si>
   <si>
     <t xml:space="preserve">LIST OF COLORANTS ALLOWED IN COSMETIC PRODUCTS</t>

--- a/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
+++ b/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="809">
   <si>
-    <t xml:space="preserve">File creation date: 15/09/2026</t>
+    <t xml:space="preserve">File creation date: 16/09/2026</t>
   </si>
   <si>
     <t xml:space="preserve">ANNEX IV,Last update: 14/09/2026</t>

--- a/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
+++ b/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="809">
   <si>
-    <t xml:space="preserve">File creation date: 16/09/2026</t>
+    <t xml:space="preserve">File creation date: 17/09/2026</t>
   </si>
   <si>
     <t xml:space="preserve">ANNEX IV,Last update: 14/09/2026</t>

--- a/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
+++ b/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="809">
   <si>
-    <t xml:space="preserve">File creation date: 17/09/2026</t>
+    <t xml:space="preserve">File creation date: 18/09/2026</t>
   </si>
   <si>
     <t xml:space="preserve">ANNEX IV,Last update: 14/09/2026</t>

--- a/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
+++ b/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="809">
   <si>
-    <t xml:space="preserve">File creation date: 18/09/2026</t>
+    <t xml:space="preserve">File creation date: 19/09/2026</t>
   </si>
   <si>
     <t xml:space="preserve">ANNEX IV,Last update: 14/09/2026</t>

--- a/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
+++ b/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="809">
   <si>
-    <t xml:space="preserve">File creation date: 19/09/2026</t>
+    <t xml:space="preserve">File creation date: 20/09/2026</t>
   </si>
   <si>
     <t xml:space="preserve">ANNEX IV,Last update: 14/09/2026</t>

--- a/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
+++ b/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="809">
   <si>
-    <t xml:space="preserve">File creation date: 20/09/2026</t>
+    <t xml:space="preserve">File creation date: 21/09/2026</t>
   </si>
   <si>
     <t xml:space="preserve">ANNEX IV,Last update: 14/09/2026</t>

--- a/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
+++ b/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="809">
   <si>
-    <t xml:space="preserve">File creation date: 21/09/2026</t>
+    <t xml:space="preserve">File creation date: 22/09/2026</t>
   </si>
   <si>
     <t xml:space="preserve">ANNEX IV,Last update: 14/09/2026</t>

--- a/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
+++ b/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
@@ -22,10 +22,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="809">
   <si>
-    <t xml:space="preserve">File creation date: 22/09/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANNEX IV,Last update: 14/09/2026</t>
+    <t xml:space="preserve">File creation date: 23/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANNEX IV,Last update: 22/09/2026</t>
   </si>
   <si>
     <t xml:space="preserve">LIST OF COLORANTS ALLOWED IN COSMETIC PRODUCTS</t>

--- a/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
+++ b/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="809">
   <si>
-    <t xml:space="preserve">File creation date: 23/09/2026</t>
+    <t xml:space="preserve">File creation date: 24/09/2026</t>
   </si>
   <si>
     <t xml:space="preserve">ANNEX IV,Last update: 22/09/2026</t>

--- a/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
+++ b/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
@@ -22,10 +22,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="809">
   <si>
-    <t xml:space="preserve">File creation date: 24/09/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANNEX IV,Last update: 22/09/2026</t>
+    <t xml:space="preserve">File creation date: 25/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANNEX IV,Last update: 24/09/2026</t>
   </si>
   <si>
     <t xml:space="preserve">LIST OF COLORANTS ALLOWED IN COSMETIC PRODUCTS</t>

--- a/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
+++ b/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="809">
   <si>
-    <t xml:space="preserve">File creation date: 25/09/2026</t>
+    <t xml:space="preserve">File creation date: 26/09/2026</t>
   </si>
   <si>
     <t xml:space="preserve">ANNEX IV,Last update: 24/09/2026</t>

--- a/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
+++ b/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="809">
   <si>
-    <t xml:space="preserve">File creation date: 26/09/2026</t>
+    <t xml:space="preserve">File creation date: 27/09/2026</t>
   </si>
   <si>
     <t xml:space="preserve">ANNEX IV,Last update: 24/09/2026</t>

--- a/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
+++ b/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="809">
   <si>
-    <t xml:space="preserve">File creation date: 27/09/2026</t>
+    <t xml:space="preserve">File creation date: 28/09/2026</t>
   </si>
   <si>
     <t xml:space="preserve">ANNEX IV,Last update: 24/09/2026</t>

--- a/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
+++ b/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="809">
   <si>
-    <t xml:space="preserve">File creation date: 28/09/2026</t>
+    <t xml:space="preserve">File creation date: 29/09/2026</t>
   </si>
   <si>
     <t xml:space="preserve">ANNEX IV,Last update: 24/09/2026</t>

--- a/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
+++ b/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
@@ -22,10 +22,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="809">
   <si>
-    <t xml:space="preserve">File creation date: 29/09/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANNEX IV,Last update: 24/09/2026</t>
+    <t xml:space="preserve">File creation date: 30/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANNEX IV,Last update: 29/09/2026</t>
   </si>
   <si>
     <t xml:space="preserve">LIST OF COLORANTS ALLOWED IN COSMETIC PRODUCTS</t>

--- a/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
+++ b/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="809">
   <si>
-    <t xml:space="preserve">File creation date: 30/09/2026</t>
+    <t xml:space="preserve">File creation date: 01/10/2026</t>
   </si>
   <si>
     <t xml:space="preserve">ANNEX IV,Last update: 29/09/2026</t>

--- a/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
+++ b/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="809">
   <si>
-    <t xml:space="preserve">File creation date: 01/10/2026</t>
+    <t xml:space="preserve">File creation date: 02/10/2026</t>
   </si>
   <si>
     <t xml:space="preserve">ANNEX IV,Last update: 29/09/2026</t>

--- a/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
+++ b/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="809">
   <si>
-    <t xml:space="preserve">File creation date: 02/10/2026</t>
+    <t xml:space="preserve">File creation date: 03/10/2026</t>
   </si>
   <si>
     <t xml:space="preserve">ANNEX IV,Last update: 29/09/2026</t>

--- a/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
+++ b/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="809">
   <si>
-    <t xml:space="preserve">File creation date: 03/10/2026</t>
+    <t xml:space="preserve">File creation date: 04/10/2026</t>
   </si>
   <si>
     <t xml:space="preserve">ANNEX IV,Last update: 29/09/2026</t>

--- a/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
+++ b/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="809">
   <si>
-    <t xml:space="preserve">File creation date: 04/10/2026</t>
+    <t xml:space="preserve">File creation date: 05/10/2026</t>
   </si>
   <si>
     <t xml:space="preserve">ANNEX IV,Last update: 29/09/2026</t>

--- a/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
+++ b/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="809">
   <si>
-    <t xml:space="preserve">File creation date: 05/10/2026</t>
+    <t xml:space="preserve">File creation date: 06/10/2026</t>
   </si>
   <si>
     <t xml:space="preserve">ANNEX IV,Last update: 29/09/2026</t>

--- a/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
+++ b/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
@@ -22,10 +22,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="809">
   <si>
-    <t xml:space="preserve">File creation date: 06/10/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANNEX IV,Last update: 29/09/2026</t>
+    <t xml:space="preserve">File creation date: 07/10/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANNEX IV,Last update: 06/10/2026</t>
   </si>
   <si>
     <t xml:space="preserve">LIST OF COLORANTS ALLOWED IN COSMETIC PRODUCTS</t>

--- a/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
+++ b/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="809">
   <si>
-    <t xml:space="preserve">File creation date: 07/10/2026</t>
+    <t xml:space="preserve">File creation date: 08/10/2026</t>
   </si>
   <si>
     <t xml:space="preserve">ANNEX IV,Last update: 06/10/2026</t>

--- a/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
+++ b/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="809">
   <si>
-    <t xml:space="preserve">File creation date: 08/10/2026</t>
+    <t xml:space="preserve">File creation date: 09/10/2026</t>
   </si>
   <si>
     <t xml:space="preserve">ANNEX IV,Last update: 06/10/2026</t>

--- a/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
+++ b/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="809">
   <si>
-    <t xml:space="preserve">File creation date: 09/10/2026</t>
+    <t xml:space="preserve">File creation date: 10/10/2026</t>
   </si>
   <si>
     <t xml:space="preserve">ANNEX IV,Last update: 06/10/2026</t>

--- a/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
+++ b/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="809">
   <si>
-    <t xml:space="preserve">File creation date: 10/10/2026</t>
+    <t xml:space="preserve">File creation date: 11/10/2026</t>
   </si>
   <si>
     <t xml:space="preserve">ANNEX IV,Last update: 06/10/2026</t>

--- a/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
+++ b/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="809">
   <si>
-    <t xml:space="preserve">File creation date: 11/10/2026</t>
+    <t xml:space="preserve">File creation date: 12/10/2026</t>
   </si>
   <si>
     <t xml:space="preserve">ANNEX IV,Last update: 06/10/2026</t>

--- a/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
+++ b/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
@@ -22,10 +22,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="809">
   <si>
-    <t xml:space="preserve">File creation date: 12/10/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANNEX IV,Last update: 06/10/2026</t>
+    <t xml:space="preserve">File creation date: 13/10/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANNEX IV,Last update: 12/10/2026</t>
   </si>
   <si>
     <t xml:space="preserve">LIST OF COLORANTS ALLOWED IN COSMETIC PRODUCTS</t>

--- a/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
+++ b/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
@@ -22,10 +22,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="809">
   <si>
-    <t xml:space="preserve">File creation date: 13/10/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANNEX IV,Last update: 12/10/2026</t>
+    <t xml:space="preserve">File creation date: 14/10/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANNEX IV,Last update: 13/10/2026</t>
   </si>
   <si>
     <t xml:space="preserve">LIST OF COLORANTS ALLOWED IN COSMETIC PRODUCTS</t>

--- a/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
+++ b/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="809">
   <si>
-    <t xml:space="preserve">File creation date: 14/10/2026</t>
+    <t xml:space="preserve">File creation date: 15/10/2026</t>
   </si>
   <si>
     <t xml:space="preserve">ANNEX IV,Last update: 13/10/2026</t>

--- a/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
+++ b/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="809">
   <si>
-    <t xml:space="preserve">File creation date: 15/10/2026</t>
+    <t xml:space="preserve">File creation date: 16/10/2026</t>
   </si>
   <si>
     <t xml:space="preserve">ANNEX IV,Last update: 13/10/2026</t>

--- a/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
+++ b/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="809">
   <si>
-    <t xml:space="preserve">File creation date: 16/10/2026</t>
+    <t xml:space="preserve">File creation date: 17/10/2026</t>
   </si>
   <si>
     <t xml:space="preserve">ANNEX IV,Last update: 13/10/2026</t>

--- a/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
+++ b/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="809">
   <si>
-    <t xml:space="preserve">File creation date: 17/10/2026</t>
+    <t xml:space="preserve">File creation date: 18/10/2026</t>
   </si>
   <si>
     <t xml:space="preserve">ANNEX IV,Last update: 13/10/2026</t>

--- a/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
+++ b/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="809">
   <si>
-    <t xml:space="preserve">File creation date: 18/10/2026</t>
+    <t xml:space="preserve">File creation date: 19/10/2026</t>
   </si>
   <si>
     <t xml:space="preserve">ANNEX IV,Last update: 13/10/2026</t>

--- a/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
+++ b/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="809">
   <si>
-    <t xml:space="preserve">File creation date: 19/10/2026</t>
+    <t xml:space="preserve">File creation date: 20/10/2026</t>
   </si>
   <si>
     <t xml:space="preserve">ANNEX IV,Last update: 13/10/2026</t>

--- a/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
+++ b/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="809">
   <si>
-    <t xml:space="preserve">File creation date: 20/10/2026</t>
+    <t xml:space="preserve">File creation date: 21/10/2026</t>
   </si>
   <si>
     <t xml:space="preserve">ANNEX IV,Last update: 13/10/2026</t>

--- a/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
+++ b/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="809">
   <si>
-    <t xml:space="preserve">File creation date: 21/10/2026</t>
+    <t xml:space="preserve">File creation date: 22/10/2026</t>
   </si>
   <si>
     <t xml:space="preserve">ANNEX IV,Last update: 13/10/2026</t>

--- a/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
+++ b/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="809">
   <si>
-    <t xml:space="preserve">File creation date: 22/10/2026</t>
+    <t xml:space="preserve">File creation date: 23/10/2026</t>
   </si>
   <si>
     <t xml:space="preserve">ANNEX IV,Last update: 13/10/2026</t>

--- a/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
+++ b/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="809">
   <si>
-    <t xml:space="preserve">File creation date: 23/10/2026</t>
+    <t xml:space="preserve">File creation date: 24/10/2026</t>
   </si>
   <si>
     <t xml:space="preserve">ANNEX IV,Last update: 13/10/2026</t>

--- a/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
+++ b/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="809">
   <si>
-    <t xml:space="preserve">File creation date: 24/10/2026</t>
+    <t xml:space="preserve">File creation date: 25/10/2026</t>
   </si>
   <si>
     <t xml:space="preserve">ANNEX IV,Last update: 13/10/2026</t>

--- a/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
+++ b/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="809">
   <si>
-    <t xml:space="preserve">File creation date: 25/10/2026</t>
+    <t xml:space="preserve">File creation date: 26/10/2026</t>
   </si>
   <si>
     <t xml:space="preserve">ANNEX IV,Last update: 13/10/2026</t>

--- a/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
+++ b/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="809">
   <si>
-    <t xml:space="preserve">File creation date: 26/10/2026</t>
+    <t xml:space="preserve">File creation date: 27/10/2026</t>
   </si>
   <si>
     <t xml:space="preserve">ANNEX IV,Last update: 13/10/2026</t>

--- a/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
+++ b/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="809">
   <si>
-    <t xml:space="preserve">File creation date: 27/10/2026</t>
+    <t xml:space="preserve">File creation date: 28/10/2026</t>
   </si>
   <si>
     <t xml:space="preserve">ANNEX IV,Last update: 13/10/2026</t>

--- a/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
+++ b/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="809">
   <si>
-    <t xml:space="preserve">File creation date: 28/10/2026</t>
+    <t xml:space="preserve">File creation date: 29/10/2026</t>
   </si>
   <si>
     <t xml:space="preserve">ANNEX IV,Last update: 13/10/2026</t>

--- a/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
+++ b/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="809">
   <si>
-    <t xml:space="preserve">File creation date: 29/10/2026</t>
+    <t xml:space="preserve">File creation date: 30/10/2026</t>
   </si>
   <si>
     <t xml:space="preserve">ANNEX IV,Last update: 13/10/2026</t>

--- a/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
+++ b/RESTRICCIONES/COSING_Annex_IV_v2.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="809">
   <si>
-    <t xml:space="preserve">File creation date: 30/10/2026</t>
+    <t xml:space="preserve">File creation date: 31/10/2026</t>
   </si>
   <si>
     <t xml:space="preserve">ANNEX IV,Last update: 13/10/2026</t>
